--- a/specific-profile-img/ig/StructureDefinition-fr-imaging-request-extension.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-imaging-request-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:56:22+00:00</t>
+    <t>2026-07-31T09:38:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
